--- a/data/raw/exogenous/combustible_precio/Costo_de_Suministro_de_Combustible_($kWh)_2025.xlsx
+++ b/data/raw/exogenous/combustible_precio/Costo_de_Suministro_de_Combustible_($kWh)_2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\Dev\maestria-trabajo-integrador\data\raw\exogenous\combustible_precio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195CB22A-EF34-4964-971F-7EC60D706EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F0578B-8D0B-4D73-AAFB-D06596FF6E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00;\-#,##0.00;\-"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -87,7 +87,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -110,11 +110,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -122,12 +135,72 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -488,16 +561,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E182"/>
+  <dimension ref="A1:E213"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" style="4" customWidth="1"/>
     <col min="2" max="4" width="14.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -514,7 +587,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>45658</v>
       </c>
       <c r="B2" s="1">
@@ -531,7 +604,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+      <c r="A3" s="4">
         <v>45659</v>
       </c>
       <c r="B3" s="1">
@@ -548,7 +621,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="A4" s="4">
         <v>45660</v>
       </c>
       <c r="B4" s="1">
@@ -565,7 +638,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+      <c r="A5" s="4">
         <v>45661</v>
       </c>
       <c r="B5" s="1">
@@ -582,7 +655,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+      <c r="A6" s="4">
         <v>45662</v>
       </c>
       <c r="B6" s="1">
@@ -599,7 +672,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+      <c r="A7" s="4">
         <v>45663</v>
       </c>
       <c r="B7" s="1">
@@ -616,7 +689,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+      <c r="A8" s="4">
         <v>45664</v>
       </c>
       <c r="B8" s="1">
@@ -633,7 +706,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+      <c r="A9" s="4">
         <v>45665</v>
       </c>
       <c r="B9" s="1">
@@ -650,7 +723,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+      <c r="A10" s="4">
         <v>45666</v>
       </c>
       <c r="B10" s="1">
@@ -667,7 +740,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+      <c r="A11" s="4">
         <v>45667</v>
       </c>
       <c r="B11" s="1">
@@ -684,7 +757,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+      <c r="A12" s="4">
         <v>45668</v>
       </c>
       <c r="B12" s="1">
@@ -701,7 +774,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+      <c r="A13" s="4">
         <v>45669</v>
       </c>
       <c r="B13" s="1">
@@ -718,7 +791,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+      <c r="A14" s="4">
         <v>45670</v>
       </c>
       <c r="B14" s="1">
@@ -735,7 +808,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
+      <c r="A15" s="4">
         <v>45671</v>
       </c>
       <c r="B15" s="1">
@@ -752,7 +825,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+      <c r="A16" s="4">
         <v>45672</v>
       </c>
       <c r="B16" s="1">
@@ -769,7 +842,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+      <c r="A17" s="4">
         <v>45673</v>
       </c>
       <c r="B17" s="1">
@@ -786,7 +859,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+      <c r="A18" s="4">
         <v>45674</v>
       </c>
       <c r="B18" s="1">
@@ -803,7 +876,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+      <c r="A19" s="4">
         <v>45675</v>
       </c>
       <c r="B19" s="1">
@@ -820,7 +893,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
+      <c r="A20" s="4">
         <v>45676</v>
       </c>
       <c r="B20" s="1">
@@ -837,7 +910,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
+      <c r="A21" s="4">
         <v>45677</v>
       </c>
       <c r="B21" s="1">
@@ -854,7 +927,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
+      <c r="A22" s="4">
         <v>45678</v>
       </c>
       <c r="B22" s="1">
@@ -871,7 +944,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
+      <c r="A23" s="4">
         <v>45679</v>
       </c>
       <c r="B23" s="1">
@@ -888,7 +961,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+      <c r="A24" s="4">
         <v>45680</v>
       </c>
       <c r="B24" s="1">
@@ -905,7 +978,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
+      <c r="A25" s="4">
         <v>45681</v>
       </c>
       <c r="B25" s="1">
@@ -922,7 +995,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
+      <c r="A26" s="4">
         <v>45682</v>
       </c>
       <c r="B26" s="1">
@@ -939,7 +1012,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
+      <c r="A27" s="4">
         <v>45683</v>
       </c>
       <c r="B27" s="1">
@@ -956,7 +1029,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
+      <c r="A28" s="4">
         <v>45684</v>
       </c>
       <c r="B28" s="1">
@@ -973,7 +1046,7 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
+      <c r="A29" s="4">
         <v>45685</v>
       </c>
       <c r="B29" s="1">
@@ -990,7 +1063,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
+      <c r="A30" s="4">
         <v>45686</v>
       </c>
       <c r="B30" s="1">
@@ -1007,7 +1080,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
+      <c r="A31" s="4">
         <v>45687</v>
       </c>
       <c r="B31" s="1">
@@ -1024,7 +1097,7 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
+      <c r="A32" s="4">
         <v>45688</v>
       </c>
       <c r="B32" s="1">
@@ -1041,7 +1114,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
+      <c r="A33" s="4">
         <v>45689</v>
       </c>
       <c r="B33" s="1">
@@ -1058,7 +1131,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
+      <c r="A34" s="4">
         <v>45690</v>
       </c>
       <c r="B34" s="1">
@@ -1075,7 +1148,7 @@
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
+      <c r="A35" s="4">
         <v>45691</v>
       </c>
       <c r="B35" s="1">
@@ -1092,7 +1165,7 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
+      <c r="A36" s="4">
         <v>45692</v>
       </c>
       <c r="B36" s="1">
@@ -1109,7 +1182,7 @@
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
+      <c r="A37" s="4">
         <v>45693</v>
       </c>
       <c r="B37" s="1">
@@ -1126,7 +1199,7 @@
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
+      <c r="A38" s="4">
         <v>45694</v>
       </c>
       <c r="B38" s="1">
@@ -1143,7 +1216,7 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
+      <c r="A39" s="4">
         <v>45695</v>
       </c>
       <c r="B39" s="1">
@@ -1160,7 +1233,7 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
+      <c r="A40" s="4">
         <v>45696</v>
       </c>
       <c r="B40" s="1">
@@ -1177,7 +1250,7 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
+      <c r="A41" s="4">
         <v>45697</v>
       </c>
       <c r="B41" s="1">
@@ -1194,7 +1267,7 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
+      <c r="A42" s="4">
         <v>45698</v>
       </c>
       <c r="B42" s="1">
@@ -1211,7 +1284,7 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
+      <c r="A43" s="4">
         <v>45699</v>
       </c>
       <c r="B43" s="1">
@@ -1228,7 +1301,7 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
+      <c r="A44" s="4">
         <v>45700</v>
       </c>
       <c r="B44" s="1">
@@ -1245,7 +1318,7 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
+      <c r="A45" s="4">
         <v>45701</v>
       </c>
       <c r="B45" s="1">
@@ -1262,7 +1335,7 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
+      <c r="A46" s="4">
         <v>45702</v>
       </c>
       <c r="B46" s="1">
@@ -1279,7 +1352,7 @@
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
+      <c r="A47" s="4">
         <v>45703</v>
       </c>
       <c r="B47" s="1">
@@ -1296,7 +1369,7 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
+      <c r="A48" s="4">
         <v>45704</v>
       </c>
       <c r="B48" s="1">
@@ -1313,7 +1386,7 @@
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
+      <c r="A49" s="4">
         <v>45705</v>
       </c>
       <c r="B49" s="1">
@@ -1330,7 +1403,7 @@
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
+      <c r="A50" s="4">
         <v>45706</v>
       </c>
       <c r="B50" s="1">
@@ -1347,7 +1420,7 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="3">
+      <c r="A51" s="4">
         <v>45707</v>
       </c>
       <c r="B51" s="1">
@@ -1364,7 +1437,7 @@
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
+      <c r="A52" s="4">
         <v>45708</v>
       </c>
       <c r="B52" s="1">
@@ -1381,7 +1454,7 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="3">
+      <c r="A53" s="4">
         <v>45709</v>
       </c>
       <c r="B53" s="1">
@@ -1398,7 +1471,7 @@
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="3">
+      <c r="A54" s="4">
         <v>45710</v>
       </c>
       <c r="B54" s="1">
@@ -1415,7 +1488,7 @@
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="3">
+      <c r="A55" s="4">
         <v>45711</v>
       </c>
       <c r="B55" s="1">
@@ -1432,7 +1505,7 @@
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="3">
+      <c r="A56" s="4">
         <v>45712</v>
       </c>
       <c r="B56" s="1">
@@ -1449,7 +1522,7 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="3">
+      <c r="A57" s="4">
         <v>45713</v>
       </c>
       <c r="B57" s="1">
@@ -1466,7 +1539,7 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="3">
+      <c r="A58" s="4">
         <v>45714</v>
       </c>
       <c r="B58" s="1">
@@ -1483,7 +1556,7 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="3">
+      <c r="A59" s="4">
         <v>45715</v>
       </c>
       <c r="B59" s="1">
@@ -1500,7 +1573,7 @@
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="3">
+      <c r="A60" s="4">
         <v>45716</v>
       </c>
       <c r="B60" s="1">
@@ -1517,7 +1590,7 @@
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="3">
+      <c r="A61" s="4">
         <v>45717</v>
       </c>
       <c r="B61" s="1">
@@ -1534,7 +1607,7 @@
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="3">
+      <c r="A62" s="4">
         <v>45718</v>
       </c>
       <c r="B62" s="1">
@@ -1551,7 +1624,7 @@
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="3">
+      <c r="A63" s="4">
         <v>45719</v>
       </c>
       <c r="B63" s="1">
@@ -1568,7 +1641,7 @@
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="3">
+      <c r="A64" s="4">
         <v>45720</v>
       </c>
       <c r="B64" s="1">
@@ -1585,7 +1658,7 @@
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="3">
+      <c r="A65" s="4">
         <v>45721</v>
       </c>
       <c r="B65" s="1">
@@ -1602,7 +1675,7 @@
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="3">
+      <c r="A66" s="4">
         <v>45722</v>
       </c>
       <c r="B66" s="1">
@@ -1619,7 +1692,7 @@
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="3">
+      <c r="A67" s="4">
         <v>45723</v>
       </c>
       <c r="B67" s="1">
@@ -1636,7 +1709,7 @@
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="3">
+      <c r="A68" s="4">
         <v>45724</v>
       </c>
       <c r="B68" s="1">
@@ -1653,7 +1726,7 @@
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="3">
+      <c r="A69" s="4">
         <v>45725</v>
       </c>
       <c r="B69" s="1">
@@ -1670,7 +1743,7 @@
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="3">
+      <c r="A70" s="4">
         <v>45726</v>
       </c>
       <c r="B70" s="1">
@@ -1687,7 +1760,7 @@
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="3">
+      <c r="A71" s="4">
         <v>45727</v>
       </c>
       <c r="B71" s="1">
@@ -1704,7 +1777,7 @@
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="3">
+      <c r="A72" s="4">
         <v>45728</v>
       </c>
       <c r="B72" s="1">
@@ -1721,7 +1794,7 @@
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="3">
+      <c r="A73" s="4">
         <v>45729</v>
       </c>
       <c r="B73" s="1">
@@ -1738,7 +1811,7 @@
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="3">
+      <c r="A74" s="4">
         <v>45730</v>
       </c>
       <c r="B74" s="1">
@@ -1755,7 +1828,7 @@
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="3">
+      <c r="A75" s="4">
         <v>45731</v>
       </c>
       <c r="B75" s="1">
@@ -1772,7 +1845,7 @@
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="3">
+      <c r="A76" s="4">
         <v>45732</v>
       </c>
       <c r="B76" s="1">
@@ -1789,7 +1862,7 @@
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="3">
+      <c r="A77" s="4">
         <v>45733</v>
       </c>
       <c r="B77" s="1">
@@ -1806,7 +1879,7 @@
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="3">
+      <c r="A78" s="4">
         <v>45734</v>
       </c>
       <c r="B78" s="1">
@@ -1823,7 +1896,7 @@
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="3">
+      <c r="A79" s="4">
         <v>45735</v>
       </c>
       <c r="B79" s="1">
@@ -1840,7 +1913,7 @@
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="3">
+      <c r="A80" s="4">
         <v>45736</v>
       </c>
       <c r="B80" s="1">
@@ -1857,7 +1930,7 @@
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="3">
+      <c r="A81" s="4">
         <v>45737</v>
       </c>
       <c r="B81" s="1">
@@ -1874,7 +1947,7 @@
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="3">
+      <c r="A82" s="4">
         <v>45738</v>
       </c>
       <c r="B82" s="1">
@@ -1891,7 +1964,7 @@
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="3">
+      <c r="A83" s="4">
         <v>45739</v>
       </c>
       <c r="B83" s="1">
@@ -1908,7 +1981,7 @@
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="3">
+      <c r="A84" s="4">
         <v>45740</v>
       </c>
       <c r="B84" s="1">
@@ -1925,7 +1998,7 @@
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="3">
+      <c r="A85" s="4">
         <v>45741</v>
       </c>
       <c r="B85" s="1">
@@ -1942,7 +2015,7 @@
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="3">
+      <c r="A86" s="4">
         <v>45742</v>
       </c>
       <c r="B86" s="1">
@@ -1959,7 +2032,7 @@
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="3">
+      <c r="A87" s="4">
         <v>45743</v>
       </c>
       <c r="B87" s="1">
@@ -1976,7 +2049,7 @@
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="3">
+      <c r="A88" s="4">
         <v>45744</v>
       </c>
       <c r="B88" s="1">
@@ -1993,7 +2066,7 @@
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="3">
+      <c r="A89" s="4">
         <v>45745</v>
       </c>
       <c r="B89" s="1">
@@ -2010,7 +2083,7 @@
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="3">
+      <c r="A90" s="4">
         <v>45746</v>
       </c>
       <c r="B90" s="1">
@@ -2027,7 +2100,7 @@
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="3">
+      <c r="A91" s="4">
         <v>45747</v>
       </c>
       <c r="B91" s="1">
@@ -2044,7 +2117,7 @@
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="3">
+      <c r="A92" s="4">
         <v>45748</v>
       </c>
       <c r="B92" s="1">
@@ -2061,7 +2134,7 @@
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="3">
+      <c r="A93" s="4">
         <v>45749</v>
       </c>
       <c r="B93" s="1">
@@ -2078,7 +2151,7 @@
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="3">
+      <c r="A94" s="4">
         <v>45750</v>
       </c>
       <c r="B94" s="1">
@@ -2095,7 +2168,7 @@
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="3">
+      <c r="A95" s="4">
         <v>45751</v>
       </c>
       <c r="B95" s="1">
@@ -2112,7 +2185,7 @@
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="3">
+      <c r="A96" s="4">
         <v>45752</v>
       </c>
       <c r="B96" s="1">
@@ -2129,7 +2202,7 @@
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="3">
+      <c r="A97" s="4">
         <v>45753</v>
       </c>
       <c r="B97" s="1">
@@ -2146,7 +2219,7 @@
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="3">
+      <c r="A98" s="4">
         <v>45754</v>
       </c>
       <c r="B98" s="1">
@@ -2163,7 +2236,7 @@
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="3">
+      <c r="A99" s="4">
         <v>45755</v>
       </c>
       <c r="B99" s="1">
@@ -2180,7 +2253,7 @@
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="3">
+      <c r="A100" s="4">
         <v>45756</v>
       </c>
       <c r="B100" s="1">
@@ -2197,7 +2270,7 @@
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="3">
+      <c r="A101" s="4">
         <v>45757</v>
       </c>
       <c r="B101" s="1">
@@ -2214,7 +2287,7 @@
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="3">
+      <c r="A102" s="4">
         <v>45758</v>
       </c>
       <c r="B102" s="1">
@@ -2231,7 +2304,7 @@
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="3">
+      <c r="A103" s="4">
         <v>45759</v>
       </c>
       <c r="B103" s="1">
@@ -2248,7 +2321,7 @@
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="3">
+      <c r="A104" s="4">
         <v>45760</v>
       </c>
       <c r="B104" s="1">
@@ -2265,7 +2338,7 @@
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="3">
+      <c r="A105" s="4">
         <v>45761</v>
       </c>
       <c r="B105" s="1">
@@ -2282,7 +2355,7 @@
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="3">
+      <c r="A106" s="4">
         <v>45762</v>
       </c>
       <c r="B106" s="1">
@@ -2299,7 +2372,7 @@
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="3">
+      <c r="A107" s="4">
         <v>45763</v>
       </c>
       <c r="B107" s="1">
@@ -2316,7 +2389,7 @@
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="3">
+      <c r="A108" s="4">
         <v>45764</v>
       </c>
       <c r="B108" s="1">
@@ -2333,7 +2406,7 @@
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="3">
+      <c r="A109" s="4">
         <v>45765</v>
       </c>
       <c r="B109" s="1">
@@ -2350,7 +2423,7 @@
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="3">
+      <c r="A110" s="4">
         <v>45766</v>
       </c>
       <c r="B110" s="1">
@@ -2367,7 +2440,7 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="3">
+      <c r="A111" s="4">
         <v>45767</v>
       </c>
       <c r="B111" s="1">
@@ -2384,7 +2457,7 @@
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="3">
+      <c r="A112" s="4">
         <v>45768</v>
       </c>
       <c r="B112" s="1">
@@ -2401,7 +2474,7 @@
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="3">
+      <c r="A113" s="4">
         <v>45769</v>
       </c>
       <c r="B113" s="1">
@@ -2418,7 +2491,7 @@
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="3">
+      <c r="A114" s="4">
         <v>45770</v>
       </c>
       <c r="B114" s="1">
@@ -2435,7 +2508,7 @@
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="3">
+      <c r="A115" s="4">
         <v>45771</v>
       </c>
       <c r="B115" s="1">
@@ -2452,7 +2525,7 @@
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="3">
+      <c r="A116" s="4">
         <v>45772</v>
       </c>
       <c r="B116" s="1">
@@ -2469,7 +2542,7 @@
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="3">
+      <c r="A117" s="4">
         <v>45773</v>
       </c>
       <c r="B117" s="1">
@@ -2486,7 +2559,7 @@
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="3">
+      <c r="A118" s="4">
         <v>45774</v>
       </c>
       <c r="B118" s="1">
@@ -2503,7 +2576,7 @@
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="3">
+      <c r="A119" s="4">
         <v>45775</v>
       </c>
       <c r="B119" s="1">
@@ -2520,7 +2593,7 @@
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="3">
+      <c r="A120" s="4">
         <v>45776</v>
       </c>
       <c r="B120" s="1">
@@ -2537,7 +2610,7 @@
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="3">
+      <c r="A121" s="4">
         <v>45777</v>
       </c>
       <c r="B121" s="1">
@@ -2554,7 +2627,7 @@
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="3">
+      <c r="A122" s="4">
         <v>45778</v>
       </c>
       <c r="B122" s="1">
@@ -2571,7 +2644,7 @@
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="3">
+      <c r="A123" s="4">
         <v>45779</v>
       </c>
       <c r="B123" s="1">
@@ -2588,7 +2661,7 @@
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="3">
+      <c r="A124" s="4">
         <v>45780</v>
       </c>
       <c r="B124" s="1">
@@ -2605,7 +2678,7 @@
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="3">
+      <c r="A125" s="4">
         <v>45781</v>
       </c>
       <c r="B125" s="1">
@@ -2622,7 +2695,7 @@
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="3">
+      <c r="A126" s="4">
         <v>45782</v>
       </c>
       <c r="B126" s="1">
@@ -2639,7 +2712,7 @@
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="3">
+      <c r="A127" s="4">
         <v>45783</v>
       </c>
       <c r="B127" s="1">
@@ -2656,7 +2729,7 @@
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="3">
+      <c r="A128" s="4">
         <v>45784</v>
       </c>
       <c r="B128" s="1">
@@ -2673,7 +2746,7 @@
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="3">
+      <c r="A129" s="4">
         <v>45785</v>
       </c>
       <c r="B129" s="1">
@@ -2690,7 +2763,7 @@
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="3">
+      <c r="A130" s="4">
         <v>45786</v>
       </c>
       <c r="B130" s="1">
@@ -2707,7 +2780,7 @@
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="3">
+      <c r="A131" s="4">
         <v>45787</v>
       </c>
       <c r="B131" s="1">
@@ -2724,7 +2797,7 @@
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="3">
+      <c r="A132" s="4">
         <v>45788</v>
       </c>
       <c r="B132" s="1">
@@ -2741,7 +2814,7 @@
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="3">
+      <c r="A133" s="4">
         <v>45789</v>
       </c>
       <c r="B133" s="1">
@@ -2758,7 +2831,7 @@
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="3">
+      <c r="A134" s="4">
         <v>45790</v>
       </c>
       <c r="B134" s="1">
@@ -2775,7 +2848,7 @@
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="3">
+      <c r="A135" s="4">
         <v>45791</v>
       </c>
       <c r="B135" s="1">
@@ -2792,7 +2865,7 @@
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="3">
+      <c r="A136" s="4">
         <v>45792</v>
       </c>
       <c r="B136" s="1">
@@ -2809,7 +2882,7 @@
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" s="3">
+      <c r="A137" s="4">
         <v>45793</v>
       </c>
       <c r="B137" s="1">
@@ -2826,7 +2899,7 @@
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" s="3">
+      <c r="A138" s="4">
         <v>45794</v>
       </c>
       <c r="B138" s="1">
@@ -2843,7 +2916,7 @@
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" s="3">
+      <c r="A139" s="4">
         <v>45795</v>
       </c>
       <c r="B139" s="1">
@@ -2860,7 +2933,7 @@
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" s="3">
+      <c r="A140" s="4">
         <v>45796</v>
       </c>
       <c r="B140" s="1">
@@ -2877,7 +2950,7 @@
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" s="3">
+      <c r="A141" s="4">
         <v>45797</v>
       </c>
       <c r="B141" s="1">
@@ -2894,7 +2967,7 @@
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" s="3">
+      <c r="A142" s="4">
         <v>45798</v>
       </c>
       <c r="B142" s="1">
@@ -2911,7 +2984,7 @@
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" s="3">
+      <c r="A143" s="4">
         <v>45799</v>
       </c>
       <c r="B143" s="1">
@@ -2928,7 +3001,7 @@
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A144" s="3">
+      <c r="A144" s="4">
         <v>45800</v>
       </c>
       <c r="B144" s="1">
@@ -2945,7 +3018,7 @@
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" s="3">
+      <c r="A145" s="4">
         <v>45801</v>
       </c>
       <c r="B145" s="1">
@@ -2962,7 +3035,7 @@
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" s="3">
+      <c r="A146" s="4">
         <v>45802</v>
       </c>
       <c r="B146" s="1">
@@ -2979,7 +3052,7 @@
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" s="3">
+      <c r="A147" s="4">
         <v>45803</v>
       </c>
       <c r="B147" s="1">
@@ -2996,7 +3069,7 @@
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" s="3">
+      <c r="A148" s="4">
         <v>45804</v>
       </c>
       <c r="B148" s="1">
@@ -3013,7 +3086,7 @@
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" s="3">
+      <c r="A149" s="4">
         <v>45805</v>
       </c>
       <c r="B149" s="1">
@@ -3030,7 +3103,7 @@
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" s="3">
+      <c r="A150" s="4">
         <v>45806</v>
       </c>
       <c r="B150" s="1">
@@ -3047,7 +3120,7 @@
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" s="3">
+      <c r="A151" s="4">
         <v>45807</v>
       </c>
       <c r="B151" s="1">
@@ -3064,7 +3137,7 @@
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" s="3">
+      <c r="A152" s="4">
         <v>45808</v>
       </c>
       <c r="B152" s="1">
@@ -3081,7 +3154,7 @@
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" s="3">
+      <c r="A153" s="4">
         <v>45809</v>
       </c>
       <c r="B153" s="1">
@@ -3098,7 +3171,7 @@
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" s="3">
+      <c r="A154" s="4">
         <v>45810</v>
       </c>
       <c r="B154" s="1">
@@ -3115,7 +3188,7 @@
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" s="3">
+      <c r="A155" s="4">
         <v>45811</v>
       </c>
       <c r="B155" s="1">
@@ -3132,7 +3205,7 @@
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" s="3">
+      <c r="A156" s="4">
         <v>45812</v>
       </c>
       <c r="B156" s="1">
@@ -3149,7 +3222,7 @@
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" s="3">
+      <c r="A157" s="4">
         <v>45813</v>
       </c>
       <c r="B157" s="1">
@@ -3166,7 +3239,7 @@
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A158" s="3">
+      <c r="A158" s="4">
         <v>45814</v>
       </c>
       <c r="B158" s="1">
@@ -3183,7 +3256,7 @@
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" s="3">
+      <c r="A159" s="4">
         <v>45815</v>
       </c>
       <c r="B159" s="1">
@@ -3200,7 +3273,7 @@
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A160" s="3">
+      <c r="A160" s="4">
         <v>45816</v>
       </c>
       <c r="B160" s="1">
@@ -3217,7 +3290,7 @@
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" s="3">
+      <c r="A161" s="4">
         <v>45817</v>
       </c>
       <c r="B161" s="1">
@@ -3234,7 +3307,7 @@
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" s="3">
+      <c r="A162" s="4">
         <v>45818</v>
       </c>
       <c r="B162" s="1">
@@ -3251,7 +3324,7 @@
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" s="3">
+      <c r="A163" s="4">
         <v>45819</v>
       </c>
       <c r="B163" s="1">
@@ -3268,7 +3341,7 @@
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" s="3">
+      <c r="A164" s="4">
         <v>45820</v>
       </c>
       <c r="B164" s="1">
@@ -3285,7 +3358,7 @@
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165" s="3">
+      <c r="A165" s="4">
         <v>45821</v>
       </c>
       <c r="B165" s="1">
@@ -3302,7 +3375,7 @@
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A166" s="3">
+      <c r="A166" s="4">
         <v>45822</v>
       </c>
       <c r="B166" s="1">
@@ -3319,7 +3392,7 @@
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" s="3">
+      <c r="A167" s="4">
         <v>45823</v>
       </c>
       <c r="B167" s="1">
@@ -3336,7 +3409,7 @@
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A168" s="3">
+      <c r="A168" s="4">
         <v>45824</v>
       </c>
       <c r="B168" s="1">
@@ -3353,7 +3426,7 @@
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169" s="3">
+      <c r="A169" s="4">
         <v>45825</v>
       </c>
       <c r="B169" s="1">
@@ -3370,7 +3443,7 @@
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A170" s="3">
+      <c r="A170" s="4">
         <v>45826</v>
       </c>
       <c r="B170" s="1">
@@ -3387,7 +3460,7 @@
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171" s="3">
+      <c r="A171" s="4">
         <v>45827</v>
       </c>
       <c r="B171" s="1">
@@ -3404,7 +3477,7 @@
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A172" s="3">
+      <c r="A172" s="4">
         <v>45828</v>
       </c>
       <c r="B172" s="1">
@@ -3421,7 +3494,7 @@
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173" s="3">
+      <c r="A173" s="4">
         <v>45829</v>
       </c>
       <c r="B173" s="1">
@@ -3438,7 +3511,7 @@
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A174" s="3">
+      <c r="A174" s="4">
         <v>45830</v>
       </c>
       <c r="B174" s="1">
@@ -3455,7 +3528,7 @@
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A175" s="3">
+      <c r="A175" s="4">
         <v>45831</v>
       </c>
       <c r="B175" s="1">
@@ -3472,7 +3545,7 @@
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A176" s="3">
+      <c r="A176" s="4">
         <v>45832</v>
       </c>
       <c r="B176" s="1">
@@ -3489,7 +3562,7 @@
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A177" s="3">
+      <c r="A177" s="4">
         <v>45833</v>
       </c>
       <c r="B177" s="1">
@@ -3506,7 +3579,7 @@
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A178" s="3">
+      <c r="A178" s="4">
         <v>45834</v>
       </c>
       <c r="B178" s="1">
@@ -3523,7 +3596,7 @@
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A179" s="3">
+      <c r="A179" s="4">
         <v>45835</v>
       </c>
       <c r="B179" s="1">
@@ -3540,7 +3613,7 @@
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A180" s="3">
+      <c r="A180" s="4">
         <v>45836</v>
       </c>
       <c r="B180" s="1">
@@ -3557,7 +3630,7 @@
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A181" s="3">
+      <c r="A181" s="4">
         <v>45837</v>
       </c>
       <c r="B181" s="1">
@@ -3574,35 +3647,577 @@
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A182" s="3">
+      <c r="A182" s="4">
         <v>45838</v>
       </c>
-      <c r="B182" s="1">
+      <c r="B182" s="5">
         <v>159.4208655098</v>
       </c>
-      <c r="C182" s="1">
+      <c r="C182" s="5">
         <v>817.93523754549994</v>
       </c>
-      <c r="D182" s="1">
+      <c r="D182" s="5">
         <v>515.62897008230004</v>
       </c>
-      <c r="E182" s="1">
+      <c r="E182" s="5">
         <v>946.61310998980002</v>
       </c>
     </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" s="4">
+        <v>45839</v>
+      </c>
+      <c r="B183" s="1">
+        <v>159.86000000000001</v>
+      </c>
+      <c r="C183" s="1">
+        <v>512.74</v>
+      </c>
+      <c r="D183" s="1">
+        <v>435.23</v>
+      </c>
+      <c r="E183" s="5">
+        <v>966.02</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" s="4">
+        <v>45840</v>
+      </c>
+      <c r="B184" s="1">
+        <v>159.86000000000001</v>
+      </c>
+      <c r="C184" s="1">
+        <v>514.83000000000004</v>
+      </c>
+      <c r="D184" s="1">
+        <v>431.05</v>
+      </c>
+      <c r="E184" s="5">
+        <v>965.91</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" s="4">
+        <v>45841</v>
+      </c>
+      <c r="B185" s="1">
+        <v>159.87</v>
+      </c>
+      <c r="C185" s="1">
+        <v>511.83</v>
+      </c>
+      <c r="D185" s="1">
+        <v>429.23</v>
+      </c>
+      <c r="E185" s="5">
+        <v>965.91</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" s="4">
+        <v>45842</v>
+      </c>
+      <c r="B186" s="1">
+        <v>159.88</v>
+      </c>
+      <c r="C186" s="1">
+        <v>514.28</v>
+      </c>
+      <c r="D186" s="1">
+        <v>429.95</v>
+      </c>
+      <c r="E186" s="5">
+        <v>965.91</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" s="4">
+        <v>45843</v>
+      </c>
+      <c r="B187" s="1">
+        <v>159.88</v>
+      </c>
+      <c r="C187" s="1">
+        <v>510.66</v>
+      </c>
+      <c r="D187" s="1">
+        <v>424.34</v>
+      </c>
+      <c r="E187" s="5">
+        <v>965.91</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" s="4">
+        <v>45844</v>
+      </c>
+      <c r="B188" s="1">
+        <v>159.88</v>
+      </c>
+      <c r="C188" s="1">
+        <v>509.91</v>
+      </c>
+      <c r="D188" s="1">
+        <v>423.7</v>
+      </c>
+      <c r="E188" s="5">
+        <v>965.91</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" s="4">
+        <v>45845</v>
+      </c>
+      <c r="B189" s="1">
+        <v>159.88999999999999</v>
+      </c>
+      <c r="C189" s="1">
+        <v>527.91</v>
+      </c>
+      <c r="D189" s="1">
+        <v>429.72</v>
+      </c>
+      <c r="E189" s="5">
+        <v>965.91</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" s="4">
+        <v>45846</v>
+      </c>
+      <c r="B190" s="1">
+        <v>159.88999999999999</v>
+      </c>
+      <c r="C190" s="1">
+        <v>512.78</v>
+      </c>
+      <c r="D190" s="1">
+        <v>427.34</v>
+      </c>
+      <c r="E190" s="5">
+        <v>965.86</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" s="4">
+        <v>45847</v>
+      </c>
+      <c r="B191" s="1">
+        <v>159.9</v>
+      </c>
+      <c r="C191" s="1">
+        <v>491.24</v>
+      </c>
+      <c r="D191" s="1">
+        <v>430.5</v>
+      </c>
+      <c r="E191" s="5">
+        <v>965.86</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" s="4">
+        <v>45848</v>
+      </c>
+      <c r="B192" s="1">
+        <v>159.91</v>
+      </c>
+      <c r="C192" s="1">
+        <v>511.47</v>
+      </c>
+      <c r="D192" s="1">
+        <v>424.42</v>
+      </c>
+      <c r="E192" s="5">
+        <v>965.86</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" s="4">
+        <v>45849</v>
+      </c>
+      <c r="B193" s="1">
+        <v>159.91</v>
+      </c>
+      <c r="C193" s="1">
+        <v>511.47</v>
+      </c>
+      <c r="D193" s="1">
+        <v>426.38</v>
+      </c>
+      <c r="E193" s="5">
+        <v>965.86</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" s="4">
+        <v>45850</v>
+      </c>
+      <c r="B194" s="1">
+        <v>159.91</v>
+      </c>
+      <c r="C194" s="1">
+        <v>522.42999999999995</v>
+      </c>
+      <c r="D194" s="1">
+        <v>463.51</v>
+      </c>
+      <c r="E194" s="5">
+        <v>965.86</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" s="4">
+        <v>45851</v>
+      </c>
+      <c r="B195" s="1">
+        <v>159.91</v>
+      </c>
+      <c r="C195" s="1">
+        <v>515.05999999999995</v>
+      </c>
+      <c r="D195" s="1">
+        <v>429.28</v>
+      </c>
+      <c r="E195" s="5">
+        <v>965.86</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" s="4">
+        <v>45852</v>
+      </c>
+      <c r="B196" s="1">
+        <v>159.91999999999999</v>
+      </c>
+      <c r="C196" s="1">
+        <v>511.24</v>
+      </c>
+      <c r="D196" s="1">
+        <v>425.12</v>
+      </c>
+      <c r="E196" s="5">
+        <v>965.86</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" s="4">
+        <v>45853</v>
+      </c>
+      <c r="B197" s="1">
+        <v>159.91999999999999</v>
+      </c>
+      <c r="C197" s="1">
+        <v>510.44</v>
+      </c>
+      <c r="D197" s="1">
+        <v>417.18</v>
+      </c>
+      <c r="E197" s="5">
+        <v>965.9</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" s="4">
+        <v>45854</v>
+      </c>
+      <c r="B198" s="1">
+        <v>159.86000000000001</v>
+      </c>
+      <c r="C198" s="1">
+        <v>486.94</v>
+      </c>
+      <c r="D198" s="1">
+        <v>420.07</v>
+      </c>
+      <c r="E198" s="5">
+        <v>965.93</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" s="4">
+        <v>45855</v>
+      </c>
+      <c r="B199" s="1">
+        <v>159.81</v>
+      </c>
+      <c r="C199" s="1">
+        <v>510.22</v>
+      </c>
+      <c r="D199" s="1">
+        <v>418.9</v>
+      </c>
+      <c r="E199" s="5">
+        <v>965.93</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" s="4">
+        <v>45856</v>
+      </c>
+      <c r="B200" s="1">
+        <v>159.77000000000001</v>
+      </c>
+      <c r="C200" s="1">
+        <v>510.63</v>
+      </c>
+      <c r="D200" s="1">
+        <v>420.39</v>
+      </c>
+      <c r="E200" s="5">
+        <v>965.93</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" s="4">
+        <v>45857</v>
+      </c>
+      <c r="B201" s="1">
+        <v>159.72999999999999</v>
+      </c>
+      <c r="C201" s="1">
+        <v>510.71</v>
+      </c>
+      <c r="D201" s="1">
+        <v>423.38</v>
+      </c>
+      <c r="E201" s="5">
+        <v>965.93</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" s="4">
+        <v>45858</v>
+      </c>
+      <c r="B202" s="1">
+        <v>159.72999999999999</v>
+      </c>
+      <c r="C202" s="1">
+        <v>508.61</v>
+      </c>
+      <c r="D202" s="1">
+        <v>418.35</v>
+      </c>
+      <c r="E202" s="5">
+        <v>965.93</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" s="4">
+        <v>45859</v>
+      </c>
+      <c r="B203" s="1">
+        <v>159.68</v>
+      </c>
+      <c r="C203" s="1">
+        <v>497.39</v>
+      </c>
+      <c r="D203" s="1">
+        <v>425.35</v>
+      </c>
+      <c r="E203" s="5">
+        <v>965.96</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A204" s="4">
+        <v>45860</v>
+      </c>
+      <c r="B204" s="1">
+        <v>159.62</v>
+      </c>
+      <c r="C204" s="1">
+        <v>516.26</v>
+      </c>
+      <c r="D204" s="1">
+        <v>420.56</v>
+      </c>
+      <c r="E204" s="5">
+        <v>965.96</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A205" s="4">
+        <v>45861</v>
+      </c>
+      <c r="B205" s="1">
+        <v>159.51</v>
+      </c>
+      <c r="C205" s="1">
+        <v>481.68</v>
+      </c>
+      <c r="D205" s="1">
+        <v>423.97</v>
+      </c>
+      <c r="E205" s="5">
+        <v>950.99</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" s="4">
+        <v>45862</v>
+      </c>
+      <c r="B206" s="1">
+        <v>159.41</v>
+      </c>
+      <c r="C206" s="1">
+        <v>512.61</v>
+      </c>
+      <c r="D206" s="1">
+        <v>425.23</v>
+      </c>
+      <c r="E206" s="5">
+        <v>965.96</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207" s="4">
+        <v>45863</v>
+      </c>
+      <c r="B207" s="1">
+        <v>159.34</v>
+      </c>
+      <c r="C207" s="1">
+        <v>506.57</v>
+      </c>
+      <c r="D207" s="1">
+        <v>423.35</v>
+      </c>
+      <c r="E207" s="5">
+        <v>965.96</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208" s="4">
+        <v>45864</v>
+      </c>
+      <c r="B208" s="1">
+        <v>159.19999999999999</v>
+      </c>
+      <c r="C208" s="1">
+        <v>517.83000000000004</v>
+      </c>
+      <c r="D208" s="1">
+        <v>421.47</v>
+      </c>
+      <c r="E208" s="5">
+        <v>965.99</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" s="4">
+        <v>45865</v>
+      </c>
+      <c r="B209" s="1">
+        <v>159.19999999999999</v>
+      </c>
+      <c r="C209" s="1">
+        <v>498.47</v>
+      </c>
+      <c r="D209" s="1">
+        <v>426.08</v>
+      </c>
+      <c r="E209" s="5">
+        <v>965.99</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210" s="4">
+        <v>45866</v>
+      </c>
+      <c r="B210" s="1">
+        <v>159.01</v>
+      </c>
+      <c r="C210" s="1">
+        <v>484.29</v>
+      </c>
+      <c r="D210" s="1">
+        <v>423.49</v>
+      </c>
+      <c r="E210" s="5">
+        <v>966.01</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211" s="4">
+        <v>45867</v>
+      </c>
+      <c r="B211" s="1">
+        <v>158.88999999999999</v>
+      </c>
+      <c r="C211" s="1">
+        <v>478.43</v>
+      </c>
+      <c r="D211" s="1">
+        <v>444.35</v>
+      </c>
+      <c r="E211" s="5">
+        <v>966.01</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212" s="4">
+        <v>45868</v>
+      </c>
+      <c r="B212" s="1">
+        <v>158.9</v>
+      </c>
+      <c r="C212" s="1">
+        <v>481.14</v>
+      </c>
+      <c r="D212" s="1">
+        <v>424.98</v>
+      </c>
+      <c r="E212" s="5">
+        <v>966.01</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213" s="4">
+        <v>45869</v>
+      </c>
+      <c r="B213" s="5">
+        <v>158.68</v>
+      </c>
+      <c r="C213" s="5">
+        <v>483.77</v>
+      </c>
+      <c r="D213" s="5">
+        <v>432.52</v>
+      </c>
+      <c r="E213" s="5">
+        <v>966.01</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A182">
+  <conditionalFormatting sqref="A2:A213">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="notEqual">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:F182">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="notEqual">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:XFD1048576">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A183:A213">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="notEqual">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:F182">
+  <conditionalFormatting sqref="E183:E213">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="notEqual">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="B213:D213">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="notEqual">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
